--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5131931d6ca54ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R88975b17002c494b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R88975b17002c494b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bb3cb9eb2044c21"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bb3cb9eb2044c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc129c65cae7a4bdd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc129c65cae7a4bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R577fc9e9ed824dcf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/inputs/x-comment.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R577fc9e9ed824dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec40e65c005949d7"/>
   </x:sheets>
 </x:workbook>
 </file>
